--- a/public/post/event/Schedule.xlsx
+++ b/public/post/event/Schedule.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/xiaotaoshen/github/scpa/content/post/2022_01_08_scpa_jc/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4D64CBEC-99B6-214C-B643-ED6E13C329B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BF1AD16E-C7BF-5E4E-AC7D-5E0B67A50C88}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="38400" windowHeight="21100" xr2:uid="{998E4D96-DBC7-A140-8B86-2BDD4638C79D}"/>
   </bookViews>
@@ -900,7 +900,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="17" spans="1:4" ht="51" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A17" s="1">
         <v>44092</v>
       </c>
